--- a/scenario/psp/skus.xlsx
+++ b/scenario/psp/skus.xlsx
@@ -64368,7 +64368,7 @@
         </is>
       </c>
       <c r="C2284" t="n">
-        <v>0.7</v>
+        <v>20</v>
       </c>
       <c r="D2284" t="n">
         <v>100</v>
